--- a/data/trans_orig/P70D_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P70D_R-Clase-trans_orig.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:W22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con capacidad laboral &lt;=6 (Likert 0 a 10) en 2023</t>
+          <t>Población con capacidad laboral &lt;=6 (Likert 0 a 10) en 2023 (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5527</t>
+          <t>5294</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20939</t>
+          <t>21747</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7678</t>
+          <t>8143</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20227</t>
+          <t>20107</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16568</t>
+          <t>16871</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>36989</t>
+          <t>38091</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,7%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>330974</t>
+          <t>330166</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>346386</t>
+          <t>346619</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>296154</t>
+          <t>296274</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>308703</t>
+          <t>308238</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>631305</t>
+          <t>630203</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>651726</t>
+          <t>651423</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,48%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4589</t>
+          <t>4631</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19244</t>
+          <t>17978</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3948</t>
+          <t>3495</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13457</t>
+          <t>13639</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10627</t>
+          <t>10331</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27786</t>
+          <t>28261</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>285132</t>
+          <t>286398</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>299787</t>
+          <t>299745</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>238628</t>
+          <t>238446</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>248137</t>
+          <t>248590</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>528675</t>
+          <t>528200</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>545834</t>
+          <t>546130</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,14%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>466</t>
+          <t>611</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17414</t>
+          <t>17884</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>2648</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9695</t>
+          <t>9919</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2168</t>
+          <t>3089</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25741</t>
+          <t>24389</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>471074</t>
+          <t>470604</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>488022</t>
+          <t>487877</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,9%</t>
+          <t>99,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>63517</t>
+          <t>63293</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>70731</t>
+          <t>70564</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>535959</t>
+          <t>537311</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>559532</t>
+          <t>558611</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,45%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28091</t>
+          <t>28446</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>52683</t>
+          <t>52914</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17990</t>
+          <t>16617</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35663</t>
+          <t>34678</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>51243</t>
+          <t>50827</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>79867</t>
+          <t>80549</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,17%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>506947</t>
+          <t>506716</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>531539</t>
+          <t>531184</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>390258</t>
+          <t>391243</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>407931</t>
+          <t>409304</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>905684</t>
+          <t>905002</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>934308</t>
+          <t>934724</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,84%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5278</t>
+          <t>6110</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18587</t>
+          <t>18359</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16022</t>
+          <t>16427</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>50103</t>
+          <t>50962</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>25988</t>
+          <t>26425</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>60895</t>
+          <t>61927</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,13%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>219593</t>
+          <t>219821</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>232902</t>
+          <t>232070</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>322835</t>
+          <t>321976</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>356916</t>
+          <t>356511</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>550223</t>
+          <t>549191</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>585130</t>
+          <t>584693</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,68%</t>
         </is>
       </c>
     </row>
@@ -2425,7 +2425,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2435,107 +2435,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>80</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>76904</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>50004</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>97862</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>119</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>81728</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>65287</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>103828</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>199</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>158631</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>119093</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>187551</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,54%</t>
         </is>
       </c>
     </row>
@@ -2548,107 +2548,107 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1568</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1865684</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1844726</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1892584</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1876</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1358809</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1336709</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1375250</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3444</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3224493</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3195573</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3264031</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,48%</t>
         </is>
       </c>
     </row>
@@ -2661,462 +2661,119 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1648</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1942588</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1942588</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1942588</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1440537</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1440537</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1440537</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3643</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3383124</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3383124</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3383124</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>76904</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>50024</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>99937</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>3,96%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>2,58%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>5,14%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>81728</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>63397</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>103846</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>5,67%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>4,4%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>7,21%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>199</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>158631</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>121832</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>188269</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>4,69%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>3,6%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>5,56%</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n"/>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>1568</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>1865684</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>1842651</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>1892564</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>96,04%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>94,86%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>97,42%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1876</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>1358809</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>1336691</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>1377140</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>94,33%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>92,79%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>95,6%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>3444</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>3224493</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>3194855</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>3261292</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>95,31%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>94,44%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>96,4%</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n"/>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>1648</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>1942588</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>1942588</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>1942588</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>1995</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>1440537</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>1440537</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>1440537</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>3643</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>3383124</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>3383124</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>3383124</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
@@ -3126,7 +2783,6 @@
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
-    <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trans_orig/P70D_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P70D_R-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>11542</t>
+          <t>12087</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5294</t>
+          <t>5535</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21747</t>
+          <t>22241</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>13152</t>
+          <t>14163</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8143</t>
+          <t>8956</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20107</t>
+          <t>22375</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>24693</t>
+          <t>26250</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16871</t>
+          <t>17498</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38091</t>
+          <t>37667</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,23%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>340371</t>
+          <t>370725</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>330166</t>
+          <t>360571</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>346619</t>
+          <t>377277</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>303229</t>
+          <t>323670</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>296274</t>
+          <t>315458</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>308238</t>
+          <t>328877</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>643601</t>
+          <t>694395</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>630203</t>
+          <t>682978</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>651423</t>
+          <t>703147</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,57%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>351913</t>
+          <t>382812</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>351913</t>
+          <t>382812</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>351913</t>
+          <t>382812</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>316381</t>
+          <t>337833</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>316381</t>
+          <t>337833</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>316381</t>
+          <t>337833</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>668294</t>
+          <t>720645</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>668294</t>
+          <t>720645</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>668294</t>
+          <t>720645</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9369</t>
+          <t>9995</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4631</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17978</t>
+          <t>19480</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7664</t>
+          <t>8542</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3495</t>
+          <t>4306</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13639</t>
+          <t>15117</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>17033</t>
+          <t>18537</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10331</t>
+          <t>11598</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28261</t>
+          <t>29181</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,91%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>295007</t>
+          <t>311765</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>286398</t>
+          <t>302280</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>299745</t>
+          <t>317045</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>244421</t>
+          <t>264311</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>238446</t>
+          <t>257736</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>248590</t>
+          <t>268547</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>539428</t>
+          <t>576075</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>528200</t>
+          <t>565431</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>546130</t>
+          <t>583014</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,05%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>304376</t>
+          <t>321760</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>304376</t>
+          <t>321760</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>304376</t>
+          <t>321760</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>252085</t>
+          <t>272853</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>252085</t>
+          <t>272853</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>252085</t>
+          <t>272853</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>556461</t>
+          <t>594612</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>556461</t>
+          <t>594612</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>556461</t>
+          <t>594612</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>6663</t>
+          <t>6655</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>2612</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17884</t>
+          <t>12799</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>5408</t>
+          <t>5661</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2648</t>
+          <t>2789</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9919</t>
+          <t>10005</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>12071</t>
+          <t>12315</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3089</t>
+          <t>7169</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24389</t>
+          <t>19893</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>5,62%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>481825</t>
+          <t>264454</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>470604</t>
+          <t>258310</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>487877</t>
+          <t>268497</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>67804</t>
+          <t>77309</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>63293</t>
+          <t>72965</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>70564</t>
+          <t>80181</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>549629</t>
+          <t>341764</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>537311</t>
+          <t>334186</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>558611</t>
+          <t>346910</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>97,98%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>488488</t>
+          <t>271109</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>488488</t>
+          <t>271109</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>488488</t>
+          <t>271109</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>73212</t>
+          <t>82970</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>73212</t>
+          <t>82970</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>73212</t>
+          <t>82970</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>561700</t>
+          <t>354079</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>561700</t>
+          <t>354079</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>561700</t>
+          <t>354079</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>38723</t>
+          <t>40391</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28446</t>
+          <t>28005</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>52914</t>
+          <t>54716</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>25248</t>
+          <t>26792</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16617</t>
+          <t>18516</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34678</t>
+          <t>37069</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>63971</t>
+          <t>67183</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>50827</t>
+          <t>51758</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>80549</t>
+          <t>84143</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>7,66%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>520907</t>
+          <t>580141</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>506716</t>
+          <t>565816</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>531184</t>
+          <t>592527</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>400673</t>
+          <t>451103</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>391243</t>
+          <t>440826</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>409304</t>
+          <t>459379</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>921580</t>
+          <t>1031245</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>905002</t>
+          <t>1014285</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>934724</t>
+          <t>1046670</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>95,29%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>559630</t>
+          <t>620532</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>559630</t>
+          <t>620532</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>559630</t>
+          <t>620532</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>425921</t>
+          <t>477895</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>425921</t>
+          <t>477895</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>425921</t>
+          <t>477895</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>985551</t>
+          <t>1098428</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>985551</t>
+          <t>1098428</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>985551</t>
+          <t>1098428</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>10608</t>
+          <t>13912</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6110</t>
+          <t>7601</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18359</t>
+          <t>22734</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>30255</t>
+          <t>32480</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16427</t>
+          <t>23912</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>50962</t>
+          <t>43656</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>40863</t>
+          <t>46393</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>26425</t>
+          <t>34583</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>61927</t>
+          <t>60787</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>9,81%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>227572</t>
+          <t>292929</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>219821</t>
+          <t>284107</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>232070</t>
+          <t>299240</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>342683</t>
+          <t>280488</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>321976</t>
+          <t>269312</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>356511</t>
+          <t>289056</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>89,62%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>86,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>570255</t>
+          <t>573417</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>549191</t>
+          <t>559023</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>584693</t>
+          <t>585227</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>94,42%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>238180</t>
+          <t>306841</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>238180</t>
+          <t>306841</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>238180</t>
+          <t>306841</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>372938</t>
+          <t>312968</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>372938</t>
+          <t>312968</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>372938</t>
+          <t>312968</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>611118</t>
+          <t>619810</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>611118</t>
+          <t>619810</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>611118</t>
+          <t>619810</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,102 +2440,102 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>76904</t>
+          <t>83039</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>50004</t>
+          <t>67261</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>97862</t>
+          <t>104593</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
+          <t>5,5%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>87638</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>72124</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>106154</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>5,9%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>4,86%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>7,15%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>170677</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>145878</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>197282</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
           <t>5,04%</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>81728</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>65287</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>103828</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>5,67%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>4,53%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>7,21%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>199</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>158631</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>119093</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>187551</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>4,69%</t>
-        </is>
-      </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,82%</t>
         </is>
       </c>
     </row>
@@ -2553,102 +2553,102 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1865684</t>
+          <t>1820016</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1844726</t>
+          <t>1798462</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1892584</t>
+          <t>1835794</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
+          <t>94,5%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>96,47%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>1876</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>1396881</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>1378365</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>1412395</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>94,1%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>92,85%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>95,14%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>3444</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>3216897</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>3190292</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>3241696</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
           <t>94,96%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>97,43%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>1876</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>1358809</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>1336709</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>1375250</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>94,33%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>92,79%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>95,47%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>3444</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>3224493</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>3195573</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>3264031</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>95,31%</t>
-        </is>
-      </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>95,69%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1942588</t>
+          <t>1903055</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1942588</t>
+          <t>1903055</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1942588</t>
+          <t>1903055</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1440537</t>
+          <t>1484519</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1440537</t>
+          <t>1484519</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1440537</t>
+          <t>1484519</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>3383124</t>
+          <t>3387574</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3383124</t>
+          <t>3387574</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>3383124</t>
+          <t>3387574</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
